--- a/reports/18_loyal_users_invite_or_revenue_lmau.xlsx
+++ b/reports/18_loyal_users_invite_or_revenue_lmau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DIMA\ОБУЧЕНИЕ\практика\project-planet-hunt-sql-analysis\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D13D5B2-4BD3-41AB-A7FD-173FF3FE04B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4DED60-7AB0-4481-B594-B4E208C7BB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9969D163-1DE0-490F-B59A-592A9F137F61}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-419]mmmm\ yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-419]mmmm\ yyyy;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -93,14 +93,14 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <numFmt numFmtId="165" formatCode="[$-419]mmmm\ yyyy;@"/>
+      <numFmt numFmtId="164" formatCode="[$-419]mmmm\ yyyy;@"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -478,7 +478,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -627,12 +627,7 @@
       <a:schemeClr val="tx1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
